--- a/Result/profitability/3379.xlsx
+++ b/Result/profitability/3379.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM69"/>
+  <dimension ref="A1:AM70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,16 +669,16 @@
         <v>0.44</v>
       </c>
       <c r="M2" t="n">
-        <v>0.405</v>
+        <v>0.31</v>
       </c>
       <c r="N2" t="n">
-        <v>14.49</v>
+        <v>16.145</v>
       </c>
       <c r="O2" t="n">
         <v>1</v>
       </c>
       <c r="P2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q2" t="n">
         <v>0</v>
@@ -687,7 +687,7 @@
         <v>0</v>
       </c>
       <c r="S2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T2" t="n">
         <v>0</v>
@@ -780,13 +780,13 @@
         <v>0.37</v>
       </c>
       <c r="M3" t="n">
-        <v>0.42375</v>
+        <v>0.25125</v>
       </c>
       <c r="N3" t="n">
-        <v>15.725</v>
+        <v>16.9525</v>
       </c>
       <c r="O3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P3" t="n">
         <v>1</v>
@@ -795,10 +795,10 @@
         <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T3" t="n">
         <v>0</v>
@@ -899,10 +899,10 @@
         <v>0.57</v>
       </c>
       <c r="M4" t="n">
-        <v>0.39</v>
+        <v>0.3025</v>
       </c>
       <c r="N4" t="n">
-        <v>17.02</v>
+        <v>18.28375</v>
       </c>
       <c r="O4" t="n">
         <v>1</v>
@@ -1018,10 +1018,10 @@
         <v>1.17</v>
       </c>
       <c r="M5" t="n">
-        <v>0.51625</v>
+        <v>0.44625</v>
       </c>
       <c r="N5" t="n">
-        <v>17.2</v>
+        <v>18.62125</v>
       </c>
       <c r="O5" t="n">
         <v>1</v>
@@ -1137,10 +1137,10 @@
         <v>1.43</v>
       </c>
       <c r="M6" t="n">
-        <v>0.6925</v>
+        <v>0.58375</v>
       </c>
       <c r="N6" t="n">
-        <v>17.62</v>
+        <v>19.69125</v>
       </c>
       <c r="O6" t="n">
         <v>1</v>
@@ -1264,13 +1264,13 @@
         <v>0.63</v>
       </c>
       <c r="M7" t="n">
-        <v>0.73</v>
+        <v>0.46</v>
       </c>
       <c r="N7" t="n">
-        <v>18.33</v>
+        <v>19.9225</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P7" t="n">
         <v>0</v>
@@ -1391,10 +1391,10 @@
         <v>1.53</v>
       </c>
       <c r="M8" t="n">
-        <v>0.7187499999999999</v>
+        <v>0.7</v>
       </c>
       <c r="N8" t="n">
-        <v>18.735</v>
+        <v>19.63875</v>
       </c>
       <c r="O8" t="n">
         <v>1</v>
@@ -9191,6 +9191,133 @@
       </c>
       <c r="AM69" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>3379</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C70" t="n">
+        <v>114</v>
+      </c>
+      <c r="D70" t="n">
+        <v>84</v>
+      </c>
+      <c r="E70" t="n">
+        <v>30</v>
+      </c>
+      <c r="F70" t="n">
+        <v>26.26</v>
+      </c>
+      <c r="G70" t="n">
+        <v>-16</v>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>-14.41%</t>
+        </is>
+      </c>
+      <c r="I70" t="n">
+        <v>3</v>
+      </c>
+      <c r="J70" t="n">
+        <v>-13</v>
+      </c>
+      <c r="K70" t="n">
+        <v>-20</v>
+      </c>
+      <c r="L70" t="n">
+        <v>-0.54</v>
+      </c>
+      <c r="M70" t="n">
+        <v>0.2825</v>
+      </c>
+      <c r="N70" t="n">
+        <v>16.125</v>
+      </c>
+      <c r="O70" t="n">
+        <v>0</v>
+      </c>
+      <c r="P70" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q70" t="n">
+        <v>0</v>
+      </c>
+      <c r="R70" t="n">
+        <v>1</v>
+      </c>
+      <c r="S70" t="n">
+        <v>0</v>
+      </c>
+      <c r="T70" t="n">
+        <v>0</v>
+      </c>
+      <c r="U70" t="n">
+        <v>0</v>
+      </c>
+      <c r="V70" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W70" t="n">
+        <v>-0.15</v>
+      </c>
+      <c r="X70" t="n">
+        <v>0.3846153846153846</v>
+      </c>
+      <c r="Y70" t="n">
+        <v>7.23</v>
+      </c>
+      <c r="Z70" t="n">
+        <v>0.3799264319495534</v>
+      </c>
+      <c r="AA70" t="n">
+        <v>-0.5600000000000001</v>
+      </c>
+      <c r="AB70" t="n">
+        <v>-28</v>
+      </c>
+      <c r="AC70" t="n">
+        <v>11.37</v>
+      </c>
+      <c r="AD70" t="n">
+        <v>0.7635997313633311</v>
+      </c>
+      <c r="AE70" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF70" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG70" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH70" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI70" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ70" t="inlineStr">
+        <is>
+          <t>EPS衰退 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK70" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL70" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM70" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
